--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/第一次真实apply_预览.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/第一次真实apply_预览.xlsx
@@ -418,7 +418,7 @@
         <v>mode</v>
       </c>
       <c r="B2" t="str">
-        <v>preview</v>
+        <v>apply</v>
       </c>
     </row>
     <row r="3">
